--- a/generated/09_style.xlsx
+++ b/generated/09_style.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1" tabColor="FF00FF00"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -63,6 +63,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF00FF00"/>
+  </sheetPr>
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
